--- a/resources/templates/standard/B1100-09.xlsx
+++ b/resources/templates/standard/B1100-09.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="11">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>특채의뢰 관리대장</t>
   </si>
@@ -539,12 +542,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -701,30 +706,30 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
@@ -743,7 +748,7 @@
       <c r="AE4" s="5"/>
       <c r="AF4" s="5"/>
       <c r="AG4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
@@ -753,12 +758,12 @@
       <c r="AM4" s="5"/>
       <c r="AN4" s="5"/>
       <c r="AO4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP4" s="5"/>
       <c r="AQ4" s="5"/>
       <c r="AR4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS4" s="5"/>
       <c r="AT4" s="5"/>
@@ -785,7 +790,7 @@
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
       <c r="P5" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
@@ -840,7 +845,7 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
@@ -895,7 +900,7 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
@@ -950,7 +955,7 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
@@ -1005,7 +1010,7 @@
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
@@ -1060,7 +1065,7 @@
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="P10" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
@@ -1115,7 +1120,7 @@
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
@@ -1170,7 +1175,7 @@
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
@@ -1225,7 +1230,7 @@
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
@@ -1280,7 +1285,7 @@
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
@@ -1335,7 +1340,7 @@
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
       <c r="P15" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
@@ -1390,7 +1395,7 @@
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
@@ -1445,7 +1450,7 @@
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
@@ -1500,7 +1505,7 @@
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
@@ -1555,7 +1560,7 @@
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
